--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_FENERBAHCE BEKO ISTANBUL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_FENERBAHCE BEKO ISTANBUL.xlsx
@@ -565,13 +565,13 @@
         <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>42.7957</v>
+        <v>45.4134</v>
       </c>
       <c r="E2" t="n">
-        <v>27.3576</v>
+        <v>29.1933</v>
       </c>
       <c r="F2" t="n">
-        <v>15.4379</v>
+        <v>16.2198</v>
       </c>
       <c r="G2" t="n">
         <v>13.3884</v>
@@ -610,13 +610,13 @@
         <v>46.1593</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9363</v>
+        <v>6.5543</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1142000000000001</v>
+        <v>1.9495</v>
       </c>
       <c r="U2" t="n">
-        <v>3.8225</v>
+        <v>4.604500000000001</v>
       </c>
       <c r="V2" t="n">
         <v>2.5076</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>24.1463</v>
+        <v>43.6677</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.554400000000001</v>
+        <v>16.5939</v>
       </c>
       <c r="F3" t="n">
-        <v>31.7008</v>
+        <v>27.0739</v>
       </c>
       <c r="G3" t="n">
-        <v>29.7727</v>
+        <v>54.1768</v>
       </c>
       <c r="H3" t="n">
-        <v>9.666599999999999</v>
+        <v>23.8234</v>
       </c>
       <c r="I3" t="n">
-        <v>20.1062</v>
+        <v>30.3536</v>
       </c>
       <c r="J3" t="n">
-        <v>28.1406</v>
+        <v>70.5487</v>
       </c>
       <c r="K3" t="n">
-        <v>8.1549</v>
+        <v>32.3933</v>
       </c>
       <c r="L3" t="n">
-        <v>19.9855</v>
+        <v>38.1554</v>
       </c>
       <c r="M3" t="n">
-        <v>1.6322</v>
+        <v>-16.3715</v>
       </c>
       <c r="N3" t="n">
-        <v>1.5121</v>
+        <v>-8.5701</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1205000000000002</v>
+        <v>-7.8015</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9279000000000002</v>
+        <v>-42.4476</v>
       </c>
       <c r="Q3" t="n">
-        <v>-48.2464</v>
+        <v>-107.8577</v>
       </c>
       <c r="R3" t="n">
-        <v>49.174</v>
+        <v>65.41069999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>23.8928</v>
+        <v>2.5183</v>
       </c>
       <c r="T3" t="n">
-        <v>11.6692</v>
+        <v>-0.4922</v>
       </c>
       <c r="U3" t="n">
-        <v>12.2234</v>
+        <v>3.0105</v>
       </c>
       <c r="V3" t="n">
-        <v>-30.447</v>
+        <v>29.4194</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8819000000000002</v>
+        <v>54.3947</v>
       </c>
       <c r="X3" t="n">
-        <v>-31.3289</v>
+        <v>-24.9753</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="n">
-        <v>23.6895</v>
+        <v>24.667</v>
       </c>
       <c r="E4" t="n">
-        <v>4.123</v>
+        <v>-6.025300000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>19.5663</v>
+        <v>30.6922</v>
       </c>
       <c r="G4" t="n">
-        <v>54.1768</v>
+        <v>28.8006</v>
       </c>
       <c r="H4" t="n">
-        <v>23.8234</v>
+        <v>28.6578</v>
       </c>
       <c r="I4" t="n">
-        <v>30.3536</v>
+        <v>0.1424000000000003</v>
       </c>
       <c r="J4" t="n">
-        <v>70.5487</v>
+        <v>39.2014</v>
       </c>
       <c r="K4" t="n">
-        <v>32.3933</v>
+        <v>33.5826</v>
       </c>
       <c r="L4" t="n">
-        <v>38.1554</v>
+        <v>5.619200000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-16.3715</v>
+        <v>-10.4009</v>
       </c>
       <c r="N4" t="n">
-        <v>-8.5701</v>
+        <v>-4.9239</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.8015</v>
+        <v>-5.4765</v>
       </c>
       <c r="P4" t="n">
-        <v>-42.4476</v>
+        <v>-38.968</v>
       </c>
       <c r="Q4" t="n">
-        <v>-107.8577</v>
+        <v>-98.8116</v>
       </c>
       <c r="R4" t="n">
-        <v>65.41069999999999</v>
+        <v>59.8438</v>
       </c>
       <c r="S4" t="n">
-        <v>-17.4599</v>
+        <v>9.1188</v>
       </c>
       <c r="T4" t="n">
-        <v>-12.9632</v>
+        <v>3.1636</v>
       </c>
       <c r="U4" t="n">
-        <v>-4.4969</v>
+        <v>5.9553</v>
       </c>
       <c r="V4" t="n">
-        <v>29.4194</v>
+        <v>25.7153</v>
       </c>
       <c r="W4" t="n">
-        <v>54.3947</v>
+        <v>50.4205</v>
       </c>
       <c r="X4" t="n">
-        <v>-24.9753</v>
+        <v>-24.7053</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>14.5414</v>
+        <v>19.9085</v>
       </c>
       <c r="E5" t="n">
-        <v>-11.4112</v>
+        <v>16.4717</v>
       </c>
       <c r="F5" t="n">
-        <v>25.9527</v>
+        <v>3.4368</v>
       </c>
       <c r="G5" t="n">
-        <v>28.8006</v>
+        <v>22.2242</v>
       </c>
       <c r="H5" t="n">
-        <v>28.6578</v>
+        <v>9.4293</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1424000000000003</v>
+        <v>12.7948</v>
       </c>
       <c r="J5" t="n">
-        <v>39.2014</v>
+        <v>26.2492</v>
       </c>
       <c r="K5" t="n">
-        <v>33.5826</v>
+        <v>10.3066</v>
       </c>
       <c r="L5" t="n">
-        <v>5.619200000000001</v>
+        <v>15.9423</v>
       </c>
       <c r="M5" t="n">
-        <v>-10.4009</v>
+        <v>-4.024900000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.9239</v>
+        <v>-0.8776000000000002</v>
       </c>
       <c r="O5" t="n">
-        <v>-5.4765</v>
+        <v>-3.1473</v>
       </c>
       <c r="P5" t="n">
-        <v>-38.968</v>
+        <v>-10.2059</v>
       </c>
       <c r="Q5" t="n">
-        <v>-98.8116</v>
+        <v>-25.2827</v>
       </c>
       <c r="R5" t="n">
-        <v>59.8438</v>
+        <v>15.0771</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0069</v>
+        <v>-1.7596</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.2221</v>
+        <v>-1.2557</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2153</v>
+        <v>-0.5036999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>25.7153</v>
+        <v>9.649800000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>50.4205</v>
+        <v>16.7609</v>
       </c>
       <c r="X5" t="n">
-        <v>-24.7053</v>
+        <v>-7.1111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>13.5233</v>
+        <v>13.1051</v>
       </c>
       <c r="E6" t="n">
-        <v>12.9135</v>
+        <v>-13.4049</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6099999999999999</v>
+        <v>26.5104</v>
       </c>
       <c r="G6" t="n">
-        <v>22.2242</v>
+        <v>29.7727</v>
       </c>
       <c r="H6" t="n">
-        <v>9.4293</v>
+        <v>9.666599999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>12.7948</v>
+        <v>20.1062</v>
       </c>
       <c r="J6" t="n">
-        <v>26.2492</v>
+        <v>28.1406</v>
       </c>
       <c r="K6" t="n">
-        <v>10.3066</v>
+        <v>8.1549</v>
       </c>
       <c r="L6" t="n">
-        <v>15.9423</v>
+        <v>19.9855</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.024900000000001</v>
+        <v>1.6322</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8776000000000002</v>
+        <v>1.5121</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.1473</v>
+        <v>0.1205000000000002</v>
       </c>
       <c r="P6" t="n">
-        <v>-10.2059</v>
+        <v>0.9279000000000002</v>
       </c>
       <c r="Q6" t="n">
-        <v>-25.2827</v>
+        <v>-48.2464</v>
       </c>
       <c r="R6" t="n">
-        <v>15.0771</v>
+        <v>49.174</v>
       </c>
       <c r="S6" t="n">
-        <v>-8.1447</v>
+        <v>12.8513</v>
       </c>
       <c r="T6" t="n">
-        <v>-4.8139</v>
+        <v>5.8186</v>
       </c>
       <c r="U6" t="n">
-        <v>-3.3308</v>
+        <v>7.032999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>9.649800000000001</v>
+        <v>-30.447</v>
       </c>
       <c r="W6" t="n">
-        <v>16.7609</v>
+        <v>0.8819000000000002</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.1111</v>
+        <v>-31.3289</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>12.2222</v>
+        <v>10.354</v>
       </c>
       <c r="E7" t="n">
-        <v>5.2963</v>
+        <v>-12.5918</v>
       </c>
       <c r="F7" t="n">
-        <v>6.925399999999999</v>
+        <v>22.9459</v>
       </c>
       <c r="G7" t="n">
-        <v>10.3892</v>
+        <v>17.3934</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7121</v>
+        <v>11.7394</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6768</v>
+        <v>5.654299999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>19.4019</v>
+        <v>28.7345</v>
       </c>
       <c r="K7" t="n">
-        <v>10.0904</v>
+        <v>19.5674</v>
       </c>
       <c r="L7" t="n">
-        <v>9.311199999999999</v>
+        <v>9.1671</v>
       </c>
       <c r="M7" t="n">
-        <v>-9.013</v>
+        <v>-11.3409</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.378399999999999</v>
+        <v>-7.8279</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.6347</v>
+        <v>-3.512899999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.7108</v>
+        <v>-14.1489</v>
       </c>
       <c r="Q7" t="n">
-        <v>-47.0866</v>
+        <v>-68.8899</v>
       </c>
       <c r="R7" t="n">
-        <v>43.3755</v>
+        <v>54.7409</v>
       </c>
       <c r="S7" t="n">
-        <v>25.2689</v>
+        <v>3.2152</v>
       </c>
       <c r="T7" t="n">
-        <v>19.4536</v>
+        <v>2.415</v>
       </c>
       <c r="U7" t="n">
-        <v>5.8153</v>
+        <v>0.7998000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-19.725</v>
+        <v>3.8945</v>
       </c>
       <c r="W7" t="n">
-        <v>13.5269</v>
+        <v>25.1482</v>
       </c>
       <c r="X7" t="n">
-        <v>-33.2519</v>
+        <v>-21.2537</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>2.119</v>
+        <v>7.8997</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.2093</v>
+        <v>-3.415400000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>9.3284</v>
+        <v>11.3149</v>
       </c>
       <c r="G8" t="n">
         <v>5.8285</v>
@@ -1078,13 +1078,13 @@
         <v>20.1804</v>
       </c>
       <c r="S8" t="n">
-        <v>-6.2682</v>
+        <v>-0.4876000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-4.821</v>
+        <v>-1.0267</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.4475</v>
+        <v>0.5393</v>
       </c>
       <c r="V8" t="n">
         <v>-3.704</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4393000000000002</v>
+        <v>4.5398</v>
       </c>
       <c r="E9" t="n">
-        <v>-14.8049</v>
+        <v>-15.2032</v>
       </c>
       <c r="F9" t="n">
-        <v>14.3658</v>
+        <v>19.7428</v>
       </c>
       <c r="G9" t="n">
-        <v>17.3934</v>
+        <v>10.8554</v>
       </c>
       <c r="H9" t="n">
-        <v>11.7394</v>
+        <v>-4.2591</v>
       </c>
       <c r="I9" t="n">
-        <v>5.654299999999999</v>
+        <v>15.1147</v>
       </c>
       <c r="J9" t="n">
-        <v>28.7345</v>
+        <v>22.3373</v>
       </c>
       <c r="K9" t="n">
-        <v>19.5674</v>
+        <v>4.161899999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>9.1671</v>
+        <v>18.1752</v>
       </c>
       <c r="M9" t="n">
-        <v>-11.3409</v>
+        <v>-11.4815</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.8279</v>
+        <v>-8.4209</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.512899999999999</v>
+        <v>-3.0605</v>
       </c>
       <c r="P9" t="n">
-        <v>-14.1489</v>
+        <v>0.2322000000000002</v>
       </c>
       <c r="Q9" t="n">
-        <v>-68.8899</v>
+        <v>-56.3646</v>
       </c>
       <c r="R9" t="n">
-        <v>54.7409</v>
+        <v>56.5966</v>
       </c>
       <c r="S9" t="n">
-        <v>-7.5786</v>
+        <v>2.8008</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2016000000000001</v>
+        <v>-1.2957</v>
       </c>
       <c r="U9" t="n">
-        <v>-7.7801</v>
+        <v>4.0964</v>
       </c>
       <c r="V9" t="n">
-        <v>3.8945</v>
+        <v>-9.348800000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>25.1482</v>
+        <v>20.1193</v>
       </c>
       <c r="X9" t="n">
-        <v>-21.2537</v>
+        <v>-29.4681</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.487000000000001</v>
+        <v>0.9395000000000007</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8101000000000003</v>
+        <v>-0.5664000000000007</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2969</v>
+        <v>1.5057</v>
       </c>
       <c r="G10" t="n">
         <v>-3.8328</v>
@@ -1234,13 +1234,13 @@
         <v>22.7316</v>
       </c>
       <c r="S10" t="n">
-        <v>5.807700000000001</v>
+        <v>7.2341</v>
       </c>
       <c r="T10" t="n">
-        <v>5.5866</v>
+        <v>4.2104</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2208000000000001</v>
+        <v>3.0231</v>
       </c>
       <c r="V10" t="n">
         <v>-10.5802</v>
@@ -1267,13 +1267,13 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9512</v>
+        <v>0.4931999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0903</v>
+        <v>-0.6436000000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1393</v>
+        <v>1.1368</v>
       </c>
       <c r="G11" t="n">
         <v>2.2056</v>
@@ -1312,13 +1312,13 @@
         <v>2.7836</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.2677</v>
+        <v>-1.8236</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0296</v>
+        <v>0.4171</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.238</v>
+        <v>-2.2406</v>
       </c>
       <c r="V11" t="n">
         <v>3.3584</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.270800000000002</v>
+        <v>-0.006199999999999539</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1643000000000017</v>
+        <v>-6.5704</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.434699999999999</v>
+        <v>6.563599999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-14.6207</v>
+        <v>10.3892</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.7172</v>
+        <v>5.7121</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.903300000000001</v>
+        <v>4.6768</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1385</v>
+        <v>19.4019</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2754000000000001</v>
+        <v>10.0904</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1368999999999996</v>
+        <v>9.311199999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-14.7592</v>
+        <v>-9.013</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.992900000000001</v>
+        <v>-4.378399999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.7664</v>
+        <v>-4.6347</v>
       </c>
       <c r="P12" t="n">
-        <v>15.5408</v>
+        <v>-3.7108</v>
       </c>
       <c r="Q12" t="n">
-        <v>-24.8193</v>
+        <v>-47.0866</v>
       </c>
       <c r="R12" t="n">
-        <v>40.3599</v>
+        <v>43.3755</v>
       </c>
       <c r="S12" t="n">
-        <v>8.3642</v>
+        <v>13.041</v>
       </c>
       <c r="T12" t="n">
-        <v>6.1608</v>
+        <v>7.5869</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2037</v>
+        <v>5.4536</v>
       </c>
       <c r="V12" t="n">
-        <v>-11.5553</v>
+        <v>-19.725</v>
       </c>
       <c r="W12" t="n">
-        <v>18.6839</v>
+        <v>13.5269</v>
       </c>
       <c r="X12" t="n">
-        <v>-30.2392</v>
+        <v>-33.2519</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.978100000000001</v>
+        <v>-0.2278999999999991</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4323000000000001</v>
+        <v>0.9279000000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.546</v>
+        <v>-1.156</v>
       </c>
       <c r="G13" t="n">
         <v>2.0751</v>
@@ -1468,13 +1468,13 @@
         <v>7.654500000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3213</v>
+        <v>0.429</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.8151</v>
+        <v>-0.4549</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.506</v>
+        <v>0.8838999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-2.9641</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. SILVA</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.6185</v>
+        <v>-1.1815</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4530000000000002</v>
+        <v>-1.6014</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1655</v>
+        <v>0.4204000000000004</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9097</v>
+        <v>-14.6207</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1967000000000002</v>
+        <v>-8.7172</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7132000000000002</v>
+        <v>-5.903300000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1327</v>
+        <v>0.1385</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4029</v>
+        <v>0.2754000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>1.7298</v>
+        <v>-0.1368999999999996</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.223</v>
+        <v>-14.7592</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.2062</v>
+        <v>-8.992900000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0167</v>
+        <v>-5.7664</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.871</v>
+        <v>15.5408</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.2214</v>
+        <v>-24.8193</v>
       </c>
       <c r="R14" t="n">
-        <v>8.3505</v>
+        <v>40.3599</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3043</v>
+        <v>9.4533</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9909</v>
+        <v>4.3949</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6865</v>
+        <v>5.0586</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9614999999999998</v>
+        <v>-11.5553</v>
       </c>
       <c r="W14" t="n">
-        <v>5.644600000000001</v>
+        <v>18.6839</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.606100000000001</v>
+        <v>-30.2392</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>C. SILVA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.6457</v>
+        <v>-4.9117</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.841799999999999</v>
+        <v>-2.073</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8039</v>
+        <v>-2.839</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.0992</v>
+        <v>0.9097</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.4062</v>
+        <v>0.1967000000000002</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.693</v>
+        <v>0.7132000000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2000999999999998</v>
+        <v>5.1327</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.8331</v>
+        <v>3.4029</v>
       </c>
       <c r="L15" t="n">
-        <v>2.0335</v>
+        <v>1.7298</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.299300000000001</v>
+        <v>-4.223</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.5729</v>
+        <v>-3.2062</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.7264</v>
+        <v>-1.0167</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5515</v>
+        <v>-4.871</v>
       </c>
       <c r="Q15" t="n">
-        <v>-15.0773</v>
+        <v>-13.2214</v>
       </c>
       <c r="R15" t="n">
-        <v>17.6286</v>
+        <v>8.3505</v>
       </c>
       <c r="S15" t="n">
-        <v>5.2939</v>
+        <v>0.011</v>
       </c>
       <c r="T15" t="n">
-        <v>3.6398</v>
+        <v>0.3709999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6541</v>
+        <v>-0.3601</v>
       </c>
       <c r="V15" t="n">
-        <v>-5.391999999999999</v>
+        <v>-0.9614999999999998</v>
       </c>
       <c r="W15" t="n">
-        <v>7.3947</v>
+        <v>5.644600000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-12.7867</v>
+        <v>-6.606100000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MAHMUTOGLU</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>-10.12</v>
+        <v>-7.429800000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.492900000000001</v>
+        <v>-4.5732</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.6271</v>
+        <v>-2.8564</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.6137</v>
+        <v>-9.0992</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.481100000000001</v>
+        <v>-6.4062</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.1326</v>
+        <v>-2.693</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.3144</v>
+        <v>0.2000999999999998</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1323</v>
+        <v>-1.8331</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.182</v>
+        <v>2.0335</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.2994</v>
+        <v>-9.299300000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3488</v>
+        <v>-4.5729</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9506</v>
+        <v>-4.7264</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0155</v>
+        <v>-15.0773</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0878</v>
+        <v>17.6286</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0422</v>
+        <v>4.5098</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6994</v>
+        <v>2.9086</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3428</v>
+        <v>1.6016</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5361</v>
+        <v>-5.391999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5361</v>
+        <v>7.3947</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>-12.7867</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>M. MAHMUTOGLU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>-11.3658</v>
+        <v>-8.8904</v>
       </c>
       <c r="E17" t="n">
-        <v>-25.5742</v>
+        <v>-5.4315</v>
       </c>
       <c r="F17" t="n">
-        <v>14.2089</v>
+        <v>-3.459</v>
       </c>
       <c r="G17" t="n">
-        <v>10.8554</v>
+        <v>-6.6137</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.2591</v>
+        <v>-2.481100000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>15.1147</v>
+        <v>-4.1326</v>
       </c>
       <c r="J17" t="n">
-        <v>22.3373</v>
+        <v>-3.3144</v>
       </c>
       <c r="K17" t="n">
-        <v>4.161899999999999</v>
+        <v>-1.1323</v>
       </c>
       <c r="L17" t="n">
-        <v>18.1752</v>
+        <v>-2.182</v>
       </c>
       <c r="M17" t="n">
-        <v>-11.4815</v>
+        <v>-3.2994</v>
       </c>
       <c r="N17" t="n">
-        <v>-8.4209</v>
+        <v>-1.3488</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.0605</v>
+        <v>-1.9506</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2322000000000002</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-56.3646</v>
+        <v>-3.0155</v>
       </c>
       <c r="R17" t="n">
-        <v>56.5966</v>
+        <v>2.0878</v>
       </c>
       <c r="S17" t="n">
-        <v>-13.1047</v>
+        <v>-0.8128</v>
       </c>
       <c r="T17" t="n">
-        <v>-11.6674</v>
+        <v>0.3621</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.4375</v>
+        <v>-1.1749</v>
       </c>
       <c r="V17" t="n">
-        <v>-9.348800000000001</v>
+        <v>-0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>20.1193</v>
+        <v>0.5361</v>
       </c>
       <c r="X17" t="n">
-        <v>-29.4681</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-29.7314</v>
+        <v>-33.4294</v>
       </c>
       <c r="E18" t="n">
-        <v>-18.7477</v>
+        <v>-23.7255</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.9832</v>
+        <v>-9.7041</v>
       </c>
       <c r="G18" t="n">
         <v>-7.4862</v>
@@ -1858,13 +1858,13 @@
         <v>15.541</v>
       </c>
       <c r="S18" t="n">
-        <v>6.6801</v>
+        <v>2.9821</v>
       </c>
       <c r="T18" t="n">
-        <v>6.188</v>
+        <v>1.2102</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4919999999999999</v>
+        <v>1.7719</v>
       </c>
       <c r="V18" t="n">
         <v>-14.0804</v>
@@ -1891,13 +1891,13 @@
         <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>63.42959999999999</v>
+        <v>114.911</v>
       </c>
       <c r="E19" t="n">
-        <v>-47.9472</v>
+        <v>-32.6388</v>
       </c>
       <c r="F19" t="n">
-        <v>111.3782</v>
+        <v>147.5487</v>
       </c>
       <c r="G19" t="n">
         <v>156.367</v>
@@ -1936,16 +1936,16 @@
         <v>527.6958000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>18.354</v>
+        <v>69.83539999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>14.973</v>
+        <v>30.2827</v>
       </c>
       <c r="U19" t="n">
-        <v>3.380999999999999</v>
+        <v>39.5522</v>
       </c>
       <c r="V19" t="n">
-        <v>-34.74939999999999</v>
+        <v>-34.74940000000001</v>
       </c>
       <c r="W19" t="n">
         <v>252.9442</v>
